--- a/xls/square_12_tri3_19.xlsx
+++ b/xls/square_12_tri3_19.xlsx
@@ -482,13 +482,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.8671898956192476</v>
+        <v>-0.8671899299253223</v>
       </c>
       <c r="J19">
-        <v>-0.736857823225412</v>
+        <v>-0.7368578505814808</v>
       </c>
       <c r="K19">
-        <v>3.725595426612032</v>
+        <v>3.725595438741577</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.4962916277242479</v>
+        <v>-0.4962916368080149</v>
       </c>
       <c r="J20">
-        <v>-0.4117689119168137</v>
+        <v>-0.4117689178370347</v>
       </c>
       <c r="K20">
-        <v>3.893142476636183</v>
+        <v>3.893142480678643</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>0.00046896987359808847</v>
+        <v>0.00046896987215219515</v>
       </c>
       <c r="J21">
-        <v>0.00010133299398272585</v>
+        <v>0.00010133299331797719</v>
       </c>
       <c r="K21">
-        <v>2.682770493878558</v>
+        <v>2.68277049363543</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00019339508088556324</v>
+        <v>-0.00019339508083283927</v>
       </c>
       <c r="J22">
-        <v>-0.00014470007312987674</v>
+        <v>-0.00014470007309828447</v>
       </c>
       <c r="K22">
-        <v>2.4219648090675125</v>
+        <v>2.4219648093083452</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0018466331257654793</v>
+        <v>-0.00184663312478087</v>
       </c>
       <c r="J23">
-        <v>-0.0012771518892069238</v>
+        <v>-0.0012771518885106598</v>
       </c>
       <c r="K23">
-        <v>2.8265995239535386</v>
+        <v>2.8265995240583304</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-8.67792986508161e-5</v>
+        <v>-8.677929864531834e-5</v>
       </c>
       <c r="J24">
-        <v>-6.73246996958608e-5</v>
+        <v>-6.732469969267803e-5</v>
       </c>
       <c r="K24">
-        <v>2.2692276046123725</v>
+        <v>2.269227604392793</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.00024088607497688773</v>
+        <v>-0.00024088607497645354</v>
       </c>
       <c r="J25">
-        <v>-0.00017604425025225271</v>
+        <v>-0.00017604425025148095</v>
       </c>
       <c r="K25">
-        <v>2.447176267793648</v>
+        <v>2.447176267731186</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00012862745513635536</v>
+        <v>-0.00012862745510601827</v>
       </c>
       <c r="J26">
-        <v>-0.00010097731714119893</v>
+        <v>-0.00010097731712610369</v>
       </c>
       <c r="K26">
-        <v>2.3628967107038066</v>
+        <v>2.362896710724885</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-3.418675226634166e-5</v>
+        <v>-3.418675226614878e-5</v>
       </c>
       <c r="J27">
-        <v>-3.028308827185714e-5</v>
+        <v>-3.02830882715196e-5</v>
       </c>
       <c r="K27">
-        <v>2.153498303877715</v>
+        <v>2.153498304067474</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-6.307456304343727e-5</v>
+        <v>-6.30745630490794e-5</v>
       </c>
       <c r="J28">
-        <v>-4.4691613009365345e-5</v>
+        <v>-4.4691613012789066e-5</v>
       </c>
       <c r="K28">
-        <v>2.1568299824707053</v>
+        <v>2.156829982537102</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>5.480636023808483e-6</v>
+        <v>5.48063601975836e-6</v>
       </c>
       <c r="J29">
-        <v>-6.1318321671451186e-6</v>
+        <v>-6.131832168639847e-6</v>
       </c>
       <c r="K29">
-        <v>2.103336330158228</v>
+        <v>2.1033363301778754</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-1.2533562449520096e-5</v>
+        <v>-1.2533562449905838e-5</v>
       </c>
       <c r="J30">
         <v>-1.4223162077242861e-5</v>
       </c>
       <c r="K30">
-        <v>2.0511140794289706</v>
+        <v>2.0511140794987983</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-2.8814753653996007e-6</v>
+        <v>-2.8814753655442506e-6</v>
       </c>
       <c r="J31">
-        <v>-2.546650836982086e-6</v>
+        <v>-2.5466508372231694e-6</v>
       </c>
       <c r="K31">
-        <v>1.6222656945936391</v>
+        <v>1.6222656947533367</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -937,13 +937,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-3.3824880964971527e-6</v>
+        <v>-3.3824880965453696e-6</v>
       </c>
       <c r="J32">
-        <v>-2.7383148860079296e-6</v>
+        <v>-2.7383148863454464e-6</v>
       </c>
       <c r="K32">
-        <v>1.6018765238127963</v>
+        <v>1.601876523612536</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_19.xlsx
+++ b/xls/square_12_tri3_19.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>400</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>1.78873137594307</v>
+      </c>
+      <c r="J17">
+        <v>-1.14017110321335</v>
+      </c>
+      <c r="K17">
+        <v>3.4061508915950887</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>400</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>-1.5887178861766418</v>
+      </c>
+      <c r="J18">
+        <v>-1.6701445838222566</v>
+      </c>
+      <c r="K18">
+        <v>2.2296295425313524</v>
+      </c>
+    </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
